--- a/TP3/salidas/tablas/TP3_Tabla_Modelos_Logit_Coef_SE_OR.xlsx
+++ b/TP3/salidas/tablas/TP3_Tabla_Modelos_Logit_Coef_SE_OR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,18 +477,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-27.0844</v>
+        <v>-1.4684</v>
       </c>
       <c r="D2" t="n">
-        <v>13862.4742</v>
+        <v>0.095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9984</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>0.2303</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,16 +506,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.2162</v>
+        <v>-1.2631</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2447</v>
+        <v>0.2367</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2964</v>
+        <v>0.2828</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,16 +535,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1314</v>
+        <v>1.0927</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2583</v>
+        <v>0.2497</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.9824</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -560,18 +564,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0441</v>
+        <v>-0.0796</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0443</v>
+        <v>0.0432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3192</v>
+        <v>0.0654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9569</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>0.9235</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -585,16 +593,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.0333</v>
+        <v>-0.0354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0388</v>
+        <v>0.0371</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3908</v>
+        <v>0.3402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9653</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -610,22 +618,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.0771</v>
+        <v>-0.0426</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0369</v>
+        <v>0.0362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0367</v>
+        <v>0.2397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9258</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.9583</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -639,16 +643,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1.3817</v>
+        <v>-1.3624</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0934</v>
+        <v>0.091</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2512</v>
+        <v>0.256</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -668,16 +672,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.4101</v>
+        <v>1.9268</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0668</v>
+        <v>0.0615</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0966</v>
+        <v>6.8675</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -697,20 +701,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1704</v>
+        <v>0.1501</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0793</v>
+        <v>0.0771</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0317</v>
+        <v>0.0517</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1858</v>
+        <v>1.1619</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -726,16 +730,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0483</v>
+        <v>-0.0396</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0804</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.6227</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0495</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -747,45 +751,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>asalariado</t>
+          <t>tiene_cobertura_salud</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.988</v>
+        <v>-2.7242</v>
       </c>
       <c r="D12" t="n">
-        <v>13862.4742</v>
+        <v>0.1179</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9985000000000001</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>193403034123.1474</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Modelo 1 - 2024</t>
+          <t>Modelo 2 - MM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tiene_cobertura_salud</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2.5906</v>
+        <v>-2.1207</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1139</v>
+        <v>0.2344</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.075</v>
+        <v>0.12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -801,20 +809,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>edad</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-26.5174</v>
+        <v>-0.9095</v>
       </c>
       <c r="D14" t="n">
-        <v>15964.494</v>
+        <v>0.5766</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9987</v>
+        <v>0.1147</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.4027</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -826,20 +834,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>edad2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.6825</v>
+        <v>0.8764</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5948</v>
+        <v>0.6051</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2512</v>
+        <v>0.1476</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5054</v>
+        <v>2.4022</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -851,20 +859,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>edad2</t>
+          <t>educ</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7143</v>
+        <v>0.0127</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6217</v>
+        <v>0.1022</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2506</v>
+        <v>0.9014</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0429</v>
+        <v>1.0127</v>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
@@ -876,20 +884,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>educ</t>
+          <t>horastrabj</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0331</v>
+        <v>0.1243</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1052</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7528</v>
+        <v>0.1274</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0337</v>
+        <v>1.1324</v>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
@@ -901,20 +909,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>horastrabj</t>
+          <t>nhogar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1066</v>
+        <v>-0.0906</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0857</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2139</v>
+        <v>0.2847</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1124</v>
+        <v>0.9134</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -926,22 +934,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nhogar</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.1141</v>
+        <v>-1.3298</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0882</v>
+        <v>0.2096</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1955</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8921</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.2645</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -951,20 +963,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>PP04C</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1.301</v>
+        <v>1.902</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2169</v>
+        <v>0.1462</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2723</v>
+        <v>6.699</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -980,26 +992,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PP04C</t>
+          <t>mujer</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.3387</v>
+        <v>-0.1384</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1614</v>
+        <v>0.1856</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.4556</v>
       </c>
       <c r="F21" t="n">
-        <v>3.8139</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>0.8707</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,20 +1017,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mujer</t>
+          <t>casado_unido</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.0959</v>
+        <v>0.0658</v>
       </c>
       <c r="D22" t="n">
-        <v>0.192</v>
+        <v>0.1954</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6175</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9086</v>
+        <v>1.068</v>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
@@ -1034,22 +1042,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>casado_unido</t>
+          <t>tiene_cobertura_salud</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.2011</v>
+        <v>-2.7344</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2021</v>
+        <v>0.2752</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3197</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2227</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>0.0649</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1059,76 +1071,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>asalariado</t>
+          <t>informal_2024</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.8721</v>
+        <v>3.0356</v>
       </c>
       <c r="D24" t="n">
-        <v>15964.494</v>
+        <v>0.206</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9988</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>63360914612.3718</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Modelo 2 - MM</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>tiene_cobertura_salud</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>-2.7474</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.2742</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0641</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Modelo 2 - MM</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>informal_2024</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3.0006</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.2182</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20.0979</v>
-      </c>
-      <c r="G26" t="inlineStr">
+        <v>20.813</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>***</t>
         </is>
